--- a/agent-improve/evals/define/judge_labelling_sheet.xlsx
+++ b/agent-improve/evals/define/judge_labelling_sheet.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-30" yWindow="75" windowWidth="28875" windowHeight="15435" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to fill" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,14 +12,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Turns'!$A$1:$L$41</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,7 +28,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial Unicode MS"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -41,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4CC"/>
+        <fgColor rgb="FFFFF4CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF4FB"/>
+        <fgColor rgb="FFEEF4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -76,9 +90,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -454,7 +476,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -462,7 +483,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -477,7 +497,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -506,7 +525,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -521,16 +539,12 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>Save the file in place when done (same name, same folder) and tell Claude Code.</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -564,10 +578,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
@@ -581,7 +595,7 @@
     <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -643,7 +657,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="390" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>20261012T124425#2</t>
@@ -685,17 +699,29 @@
           <t>pass (replayed: not run on this turn)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>coherence</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="4" t="n"/>
-    </row>
-    <row r="3">
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>right outcome, wrong reason: reason contradicts the reply text. Real fault: coach asked for a baseline the Belt already gave (23%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="165" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>20261012T124425#5</t>
@@ -737,17 +763,29 @@
           <t>pass (replayed: not run on this turn)</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>coherence</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="4" t="n"/>
-    </row>
-    <row r="4">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>judge invented a missing item: Belt said nobody else needs training. (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="409.5" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>20261012T124425#11</t>
@@ -806,11 +844,23 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="4" t="n"/>
-    </row>
-    <row r="5">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>coherence claims parroting, but the reply adds 5W2H + sample. Grader replay contradicts rubric: penalises show-first sample (required by C3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="225" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>20261012T124425#16</t>
@@ -860,11 +910,23 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="4" t="n"/>
-    </row>
-    <row r="6">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>coherence says parroting but the status is in sentence 1. Status incomplete: no done/open list (DEF-020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="255" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>20261012T124425#26</t>
@@ -904,17 +966,29 @@
           <t>pass (replayed: not run on this turn)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>coherence</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="4" t="n"/>
-    </row>
-    <row r="7">
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>sample gives away the Belt's answer (same domain: late payments); judge's reason wrong; grader passed it.A side observation for the Black Belt in you: 42,000 invoices × 23% late × £9 ≈ £87,000 a year. The Belt earlier said about £62,000. A sharp coach would ask about the gap. The coach mustn’t calculate it itself (calculations run in code), but noticing the inconsistency is good coaching. Not something to label here; just worth remembering for the coaching rubric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="300" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#2</t>
@@ -954,17 +1028,29 @@
           <t>pass (replayed: not run on this turn)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>coherence</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="4" t="n"/>
-    </row>
-    <row r="8">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ame fault as 124425#2: coach asks for a baseline the Belt already gave (23%, Jan–Jun 2026). Judge's reason (parroting) wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="360" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#9</t>
@@ -1005,17 +1091,29 @@
           <t>pass (replayed: not run on this turn)</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>coherence</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="4" t="n"/>
-    </row>
-    <row r="9">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>names missing CTQ for invoice visibility; judge's "parroting" wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409.5" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#12</t>
@@ -1084,11 +1182,23 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="4" t="n"/>
-    </row>
-    <row r="10">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>content right, but sample table duplicated in message + example block, questions ×3; judge's "parroting" wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="225" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#17</t>
@@ -1138,11 +1248,23 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="4" t="n"/>
-    </row>
-    <row r="11">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>status answered (done list + next); judge's "parroting" wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="330" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#27</t>
@@ -1182,17 +1304,29 @@
           <t>pass (replayed: not run on this turn)</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>coherence</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="4" t="n"/>
-    </row>
-    <row r="12">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>sample uses the Belt's own data (23%, 5%, 42k, £9, Tom Okafor) = gives the answer; coach computed cost of gap (ADR-0077: code computes). Grader passed it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="300" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#29</t>
@@ -1248,7 +1382,7 @@
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="4" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="409.5" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#33</t>
@@ -1313,7 +1447,7 @@
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="4" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="165" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#35</t>
@@ -1365,7 +1499,7 @@
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="4" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="409.5" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#10</t>
@@ -1432,11 +1566,19 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
       <c r="L15" s="4" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="225" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#15</t>
@@ -1476,17 +1618,29 @@
           <t>pass (replayed: not run on this turn)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>coherence</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="4" t="n"/>
-    </row>
-    <row r="17">
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>status gives only step 6/13, no done list (DEF-020); judge's "parroting" wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="409.5" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#26</t>
@@ -1541,11 +1695,23 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="4" t="n"/>
-    </row>
-    <row r="18">
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>sample uses the Belt's own data (23%, 5%, 42k, £9) + coach computes £68,040; names Lena Hart (AP, not finance). Same fault as 132229#27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#34</t>
@@ -1597,7 +1763,7 @@
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="4" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="285" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>20261012T140839#2</t>
@@ -1647,11 +1813,23 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="4" t="n"/>
-    </row>
-    <row r="20">
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>G-168 again: coach asks for baseline already given (23%). Both judges' reasons wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="409.5" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>20261012T140839#11</t>
@@ -1737,11 +1915,23 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="4" t="n"/>
-    </row>
-    <row r="21">
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>content right; table, example statement duplicated, questions ×3. Judge's "parroting" wrong; grader replay claims no follow-up questions — false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="225" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>20261012T140839#16</t>
@@ -1781,17 +1971,29 @@
           <t>pass (replayed: not run on this turn)</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
           <t>coherence</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="4" t="n"/>
-    </row>
-    <row r="22">
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>status gives only step 6/13, no done list (DEF-020); judge's "parroting" wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="409.5" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>20261012T140839#26</t>
@@ -1846,11 +2048,31 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="4" t="n"/>
-    </row>
-    <row r="23">
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>sample = Belt's own data + coach computes £68,040/£17,010 + names Tom Okafor. Third occurrence.</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="165" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>20261012T140839#34</t>
@@ -1902,7 +2124,7 @@
       <c r="K23" s="3" t="n"/>
       <c r="L23" s="4" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="120" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#18</t>
@@ -1931,7 +2153,7 @@
           <t>accepted</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>failed</t>
@@ -1947,11 +2169,23 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="4" t="n"/>
-    </row>
-    <row r="25">
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>read-back is meant to restate; grader penalises the move itself</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="409.5" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#12</t>
@@ -2007,11 +2241,24 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="4" t="n"/>
-    </row>
-    <row r="26">
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>references DMAIC (Define/Measure/Control); grader's "no methodology" false</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="409.5" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#13</t>
@@ -2052,7 +2299,7 @@
           <t>accepted</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>failed</t>
@@ -2068,11 +2315,23 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="4" t="n"/>
-    </row>
-    <row r="27">
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>statement composed only from the Belt's own 5W2H answers, then confirmed — by design; grader penalises the design</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="409.5" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#14</t>
@@ -2128,11 +2387,23 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="4" t="n"/>
-    </row>
-    <row r="28">
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>EXAMPLE block uses the Belt's own process (AP, invoice received → payment released) = gives the answer; two different samples; question ×2. Grader's "no methodology" reason wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#20</t>
@@ -2158,7 +2429,7 @@
           <t>accepted</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>failed</t>
@@ -2174,11 +2445,23 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="4" t="n"/>
-    </row>
-    <row r="29">
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>verbatim read-back for Confirm; grader calls it 'writing the problem statement' — false</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="409.5" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#9</t>
@@ -2252,11 +2535,23 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="4" t="n"/>
-    </row>
-    <row r="30">
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>good teaching, neutral sample; content duplicated (message + blocks): a format defect for code to fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="409.5" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#10</t>
@@ -2293,7 +2588,7 @@
           <t>accepted</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>failed</t>
@@ -2309,11 +2604,23 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="4" t="n"/>
-    </row>
-    <row r="31">
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>read-back offers Confirm on a CTQ with a placeholder "[specific time frame]" the coach itself calls incomplete — should challenge again. Grader's reasons wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="409.5" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#17</t>
@@ -2369,11 +2676,31 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="4" t="n"/>
-    </row>
-    <row r="32">
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE block = the Belt's exact goal (23% → &lt;5% by 31 Mar 2027). Grader right, right reason.</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="n"/>
+      <c r="R31" s="2" t="n"/>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#21</t>
@@ -2401,7 +2728,7 @@
           <t>accepted</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>failed</t>
@@ -2417,11 +2744,23 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="4" t="n"/>
-    </row>
-    <row r="33">
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>verbatim read-back incl. the Belt's correction; grader's "writing the problem statement" false</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="409.5" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#3</t>
@@ -2481,11 +2820,23 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="4" t="n"/>
-    </row>
-    <row r="34">
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>neutral sample, good teaching; duplicated (format). Grader's "no methodology" false — LSS roles explained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="165" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#3</t>
@@ -2513,7 +2864,7 @@
           <t>accepted</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>failed</t>
@@ -2529,11 +2880,23 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="4" t="n"/>
-    </row>
-    <row r="35">
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>verbatim read-back for Confirm; grader contradicts itself ("repeating" = "doing the Belt's work")</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="409.5" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#20</t>
@@ -2589,11 +2952,19 @@
           <t>grader</t>
         </is>
       </c>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L35" s="4" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="255" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#16</t>
@@ -2625,23 +2996,31 @@
           <t>accepted</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="J36" s="3" t="n"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K36" s="3" t="n"/>
-      <c r="L36" s="4" t="n"/>
-    </row>
-    <row r="37">
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>correct read-back; unnecessary explanation/example blocks on a read-back, question ×2 (format</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="409.5" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>20261012T124425#30</t>
@@ -2698,17 +3077,26 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="J37" s="3" t="n"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="n"/>
-      <c r="L37" s="4" t="n"/>
-    </row>
-    <row r="38">
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>good, neutral sample; definition repeated ×3 and one very large question (format/length)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="409.5" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#1</t>
@@ -2755,17 +3143,25 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="J38" s="3" t="n"/>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K38" s="3" t="n"/>
-      <c r="L38" s="4" t="n"/>
-    </row>
-    <row r="39">
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>good opening: overview, how it works, neutral sample, one clear question</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="240" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>20261012T134606#13</t>
@@ -2795,23 +3191,31 @@
           <t>accepted</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="J39" s="3" t="n"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K39" s="3" t="n"/>
-      <c r="L39" s="4" t="n"/>
-    </row>
-    <row r="40">
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>good read-back; number parsed in code; metric explained (DEF-018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="409.5" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>20261012T124425#28</t>
@@ -2857,17 +3261,25 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="J40" s="3" t="n"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K40" s="3" t="n"/>
-      <c r="L40" s="4" t="n"/>
-    </row>
-    <row r="41">
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>good teaching, neutral sample; definition, sample and question duplicated (format)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="409.5" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>20261012T132229#1</t>
@@ -2914,15 +3326,23 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="J41" s="3" t="n"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K41" s="3" t="n"/>
-      <c r="L41" s="4" t="n"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>good opening, neutral sample</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L41"/>
